--- a/SuppXLS/Scen_z_MACC-RSD.xlsx
+++ b/SuppXLS/Scen_z_MACC-RSD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BSuleimenov\Documents\GitHub\times-ireland-model\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4AA7109-26BA-4799-89D9-5C5CACA55AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FBCB220-1E3E-47BE-83C0-5058D0E1256B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INS" sheetId="2" r:id="rId1"/>
@@ -213,9 +213,6 @@
     <t>2021-2050</t>
   </si>
   <si>
-    <t>2024-2050</t>
-  </si>
-  <si>
     <t>region</t>
   </si>
   <si>
@@ -256,6 +253,9 @@
   </si>
   <si>
     <t>R-SW_Apt_HET_N1, R-SW_Apt_HET_N2, R-SW_Att_HET_N1, R-SW_Att_HET_N2, R-SW_Det_HET_N1, R-SW_Det_HET_N2</t>
+  </si>
+  <si>
+    <t>2020-2050</t>
   </si>
 </sst>
 </file>
@@ -681,29 +681,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" customWidth="1"/>
-    <col min="5" max="5" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" customWidth="1"/>
+    <col min="5" max="5" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="8.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
@@ -716,7 +716,7 @@
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
     </row>
-    <row r="3" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
@@ -763,7 +763,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="D4" s="7" t="s">
         <v>19</v>
       </c>
@@ -787,7 +787,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="D5" s="7" t="s">
         <v>19</v>
       </c>
@@ -811,12 +811,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="D6" s="7" t="s">
         <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -832,15 +832,15 @@
         <v>20</v>
       </c>
       <c r="X6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="D7" s="7" t="s">
         <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -859,12 +859,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="D8" s="7" t="s">
         <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -880,15 +880,15 @@
         <v>20</v>
       </c>
       <c r="X8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="D9" s="7" t="s">
         <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -904,24 +904,24 @@
         <v>21</v>
       </c>
       <c r="X9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="22:28" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="22:28" x14ac:dyDescent="0.3">
       <c r="X20" t="str">
         <f>_xlfn.TEXTJOIN(", ",TRUE,X23:X58)</f>
         <v>R-SW_Apt_HET_N1, R-SW_Apt_HET_N2, R-SW_Att_HET_N1, R-SW_Att_HET_N2, R-SW_Det_HET_N1, R-SW_Det_HET_N2</v>
       </c>
     </row>
-    <row r="22" spans="22:28" x14ac:dyDescent="0.25">
+    <row r="22" spans="22:28" x14ac:dyDescent="0.3">
       <c r="V22" t="s">
+        <v>30</v>
+      </c>
+      <c r="W22" t="s">
         <v>31</v>
       </c>
-      <c r="W22" t="s">
+      <c r="X22" t="s">
         <v>32</v>
-      </c>
-      <c r="X22" t="s">
-        <v>33</v>
       </c>
       <c r="Y22">
         <v>2018</v>
@@ -936,130 +936,130 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="23" spans="22:28" x14ac:dyDescent="0.25">
+    <row r="23" spans="22:28" x14ac:dyDescent="0.3">
       <c r="V23" t="s">
+        <v>33</v>
+      </c>
+      <c r="W23" t="s">
         <v>34</v>
       </c>
-      <c r="W23" t="s">
-        <v>35</v>
-      </c>
       <c r="X23" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y23">
+        <v>1</v>
+      </c>
+      <c r="Z23">
+        <v>1</v>
+      </c>
+      <c r="AA23">
+        <v>1</v>
+      </c>
+      <c r="AB23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="22:28" x14ac:dyDescent="0.3">
+      <c r="V24" t="s">
+        <v>33</v>
+      </c>
+      <c r="W24" t="s">
+        <v>34</v>
+      </c>
+      <c r="X24" t="s">
         <v>38</v>
       </c>
-      <c r="Y23">
-        <v>1</v>
-      </c>
-      <c r="Z23">
-        <v>1</v>
-      </c>
-      <c r="AA23">
-        <v>1</v>
-      </c>
-      <c r="AB23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="22:28" x14ac:dyDescent="0.25">
-      <c r="V24" t="s">
+      <c r="Y24">
+        <v>1</v>
+      </c>
+      <c r="Z24">
+        <v>1</v>
+      </c>
+      <c r="AA24">
+        <v>1</v>
+      </c>
+      <c r="AB24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="22:28" x14ac:dyDescent="0.3">
+      <c r="V25" t="s">
+        <v>33</v>
+      </c>
+      <c r="W25" t="s">
         <v>34</v>
       </c>
-      <c r="W24" t="s">
-        <v>35</v>
-      </c>
-      <c r="X24" t="s">
+      <c r="X25" t="s">
         <v>39</v>
       </c>
-      <c r="Y24">
-        <v>1</v>
-      </c>
-      <c r="Z24">
-        <v>1</v>
-      </c>
-      <c r="AA24">
-        <v>1</v>
-      </c>
-      <c r="AB24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="22:28" x14ac:dyDescent="0.25">
-      <c r="V25" t="s">
+      <c r="Y25">
+        <v>1</v>
+      </c>
+      <c r="Z25">
+        <v>1</v>
+      </c>
+      <c r="AA25">
+        <v>1</v>
+      </c>
+      <c r="AB25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="22:28" x14ac:dyDescent="0.3">
+      <c r="V26" t="s">
+        <v>33</v>
+      </c>
+      <c r="W26" t="s">
         <v>34</v>
       </c>
-      <c r="W25" t="s">
-        <v>35</v>
-      </c>
-      <c r="X25" t="s">
+      <c r="X26" t="s">
         <v>40</v>
       </c>
-      <c r="Y25">
-        <v>1</v>
-      </c>
-      <c r="Z25">
-        <v>1</v>
-      </c>
-      <c r="AA25">
-        <v>1</v>
-      </c>
-      <c r="AB25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="22:28" x14ac:dyDescent="0.25">
-      <c r="V26" t="s">
+      <c r="Y26">
+        <v>1</v>
+      </c>
+      <c r="Z26">
+        <v>1</v>
+      </c>
+      <c r="AA26">
+        <v>1</v>
+      </c>
+      <c r="AB26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="22:28" x14ac:dyDescent="0.3">
+      <c r="V27" t="s">
+        <v>33</v>
+      </c>
+      <c r="W27" t="s">
         <v>34</v>
       </c>
-      <c r="W26" t="s">
-        <v>35</v>
-      </c>
-      <c r="X26" t="s">
+      <c r="X27" t="s">
         <v>41</v>
       </c>
-      <c r="Y26">
-        <v>1</v>
-      </c>
-      <c r="Z26">
-        <v>1</v>
-      </c>
-      <c r="AA26">
-        <v>1</v>
-      </c>
-      <c r="AB26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="22:28" x14ac:dyDescent="0.25">
-      <c r="V27" t="s">
+      <c r="Y27">
+        <v>1</v>
+      </c>
+      <c r="Z27">
+        <v>1</v>
+      </c>
+      <c r="AA27">
+        <v>1</v>
+      </c>
+      <c r="AB27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="22:28" x14ac:dyDescent="0.3">
+      <c r="V28" t="s">
+        <v>33</v>
+      </c>
+      <c r="W28" t="s">
         <v>34</v>
       </c>
-      <c r="W27" t="s">
-        <v>35</v>
-      </c>
-      <c r="X27" t="s">
+      <c r="X28" t="s">
         <v>42</v>
-      </c>
-      <c r="Y27">
-        <v>1</v>
-      </c>
-      <c r="Z27">
-        <v>1</v>
-      </c>
-      <c r="AA27">
-        <v>1</v>
-      </c>
-      <c r="AB27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="22:28" x14ac:dyDescent="0.25">
-      <c r="V28" t="s">
-        <v>34</v>
-      </c>
-      <c r="W28" t="s">
-        <v>35</v>
-      </c>
-      <c r="X28" t="s">
-        <v>43</v>
       </c>
       <c r="Y28">
         <v>1</v>
@@ -1084,29 +1084,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="8.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
@@ -1119,7 +1119,7 @@
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
     </row>
-    <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>

--- a/SuppXLS/Scen_z_MACC-RSD.xlsx
+++ b/SuppXLS/Scen_z_MACC-RSD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BSuleimenov\Documents\GitHub\times-ireland-model\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FBCB220-1E3E-47BE-83C0-5058D0E1256B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD5313A-3E9C-4CE3-A243-853D88A9598C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -121,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="48">
   <si>
     <t>Pset_CI</t>
   </si>
@@ -256,6 +256,15 @@
   </si>
   <si>
     <t>2020-2050</t>
+  </si>
+  <si>
+    <t>R*DET*</t>
+  </si>
+  <si>
+    <t>RSDAHT,RSDAHT2</t>
+  </si>
+  <si>
+    <t>-"PRC_RESID"</t>
   </si>
 </sst>
 </file>
@@ -359,7 +368,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -374,6 +383,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -849,6 +859,9 @@
         <f t="shared" si="0"/>
         <v>R-SH_Apt_GAS_N1,R-SH_Att_GAS_N1,R-SH_Det_GAS_N1,R-SW_Apt_GAS_HHPN1,R-SW_Apt_GAS_HPN1,R-SW_Apt_GAS_HPN2,R-SW_Apt_GAS_N1,R-SW_Att_GAS_HHPN1,R-SW_Att_GAS_HPN1,R-SW_Att_GAS_HPN2,R-SW_Att_GAS_N1,R-SW_Att_GAS_N2,R-SW_Att_GAS_N3,R-SW_Det_GAS_HHPN1,R-SW_Det_GAS_HPN1,R-SW_Det_GAS_HPN2,R-SW_Det_GAS_N1,R-SW_Det_GAS_N2,R-SW_Det_GAS_N3</v>
       </c>
+      <c r="L7" t="s">
+        <v>46</v>
+      </c>
       <c r="V7" t="s">
         <v>22</v>
       </c>
@@ -905,6 +918,26 @@
       </c>
       <c r="X9" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="D10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="J10" t="s">
+        <v>45</v>
+      </c>
+      <c r="L10" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="22:28" x14ac:dyDescent="0.3">
